--- a/docs/02-domain/templates/examples/catalog_template_v1_partial.xlsx
+++ b/docs/02-domain/templates/examples/catalog_template_v1_partial.xlsx
@@ -13,7 +13,9 @@
     <sheet name="Инструкция" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="_System" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Каталог'!$A$1:$J$1000</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -198,6 +200,11 @@
     <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <t>Любые дополнительные характеристики товара текстом. Необязательно.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Список идентификаторов загруженных фотографий через `;` (например «12;15»). Заполняется автоматически карточкой товара — не редактируется вручную.</t>
       </text>
     </comment>
   </commentList>
@@ -493,10 +500,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col hidden="1" width="13" customWidth="1" min="1" max="1"/>
+    <col hidden="1" width="16" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -545,6 +561,11 @@
           <t>Дополнительные характеристики</t>
         </is>
       </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Фото</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="B2" t="inlineStr">
@@ -575,6 +596,11 @@
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -601,8 +627,14 @@
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J1000"/>
   <dataValidations count="5">
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Неизвестная товарная группа" error="Выберите товарную группу из списка (см. лист «Товарные группы»)" type="list">
       <formula1>"Фрукты,Овощи,Молочные продукты,Мясо,Рыба,Напитки,Цитрусовые,Яблоки,Бананы,Томаты,Огурцы,Картофель,Молоко,Сыр,Йогурты"</formula1>
@@ -1222,7 +1254,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>

--- a/docs/02-domain/templates/examples/catalog_template_v1_partial.xlsx
+++ b/docs/02-domain/templates/examples/catalog_template_v1_partial.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Наименование продавца</t>
+          <t>Название товара</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
@@ -1155,7 +1155,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>На листе «Каталог» одна строка = один товар. Заполните обязательные поля (выделены жёлтым): «Наименование продавца», «Товарная группа GreenMarket», «Цена», «Единица продажи», «Остаток». Товарную группу и товарную позицию выбирайте из выпадающего списка. Если подходящей товарной позиции нет — выберите «Прочее»: товар будет опубликован и пройдёт модерацию администратором. Новый товар — просто новая строка.</t>
+          <t>На листе «Каталог» одна строка = один товар. Заполните обязательные поля (выделены жёлтым): «Название товара», «Товарная группа GreenMarket», «Цена», «Единица продажи», «Остаток». Товарную группу и товарную позицию выбирайте из выпадающего списка. Если подходящей товарной позиции нет — выберите «Прочее»: товар будет опубликован и пройдёт модерацию администратором. Новый товар — просто новая строка.</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.1</t>
         </is>
       </c>
     </row>

--- a/docs/02-domain/templates/examples/catalog_template_v1_partial.xlsx
+++ b/docs/02-domain/templates/examples/catalog_template_v1_partial.xlsx
@@ -14,7 +14,7 @@
     <sheet name="_System" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Каталог'!$A$1:$J$1000</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Каталог'!$A$1:$L$1000</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -204,7 +204,17 @@
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
-        <t>Список идентификаторов загруженных фотографий через `;` (например «12;15»). Заполняется автоматически карточкой товара — не редактируется вручную.</t>
+        <t>Список идентификаторов загруженных фотографий через `;` (например «12;15»). Заполняется автоматически карточкой товара — не редактируется вручную. Без фото товар сохранится, но покупателю показан не будет — публикация сообщит о таких товарах.</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Страна, из которой привезён товар. Показывается покупателю в карточке товара. Необязательно. Пример: «Марокко».</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Дата, когда партия завезена — покупатель видит по ней свежесть товара. Формат ДД.ММ.ГГГГ, дата не может быть в будущем. Необязательно. Пример: «01.08.2026».</t>
       </text>
     </comment>
   </commentList>
@@ -500,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="16" customWidth="1" min="1" max="1"/>
@@ -513,6 +523,8 @@
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="32" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -566,6 +578,16 @@
           <t>Фото</t>
         </is>
       </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Страна происхождения</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Дата поставки</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="B2" t="inlineStr">
@@ -634,7 +656,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1000"/>
+  <autoFilter ref="A1:L1000"/>
   <dataValidations count="5">
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Неизвестная товарная группа" error="Выберите товарную группу из списка (см. лист «Товарные группы»)" type="list">
       <formula1>"Фрукты,Овощи,Молочные продукты,Мясо,Рыба,Напитки,Цитрусовые,Яблоки,Бананы,Томаты,Огурцы,Картофель,Молоко,Сыр,Йогурты"</formula1>
@@ -1254,7 +1276,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
     </row>

--- a/docs/02-domain/templates/examples/catalog_template_v1_partial.xlsx
+++ b/docs/02-domain/templates/examples/catalog_template_v1_partial.xlsx
@@ -214,7 +214,7 @@
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
       <text>
-        <t>Дата, когда партия завезена — покупатель видит по ней свежесть товара. Формат ДД.ММ.ГГГГ, дата не может быть в будущем. Необязательно. Пример: «01.08.2026».</t>
+        <t>Формат ДД.ММ.ГГГГ. Прошедшая дата означает состоявшийся завоз партии — покупатель видит по ней свежесть товара; будущая означает планируемую поставку. Необязательно. Пример: «01.08.2026».</t>
       </text>
     </comment>
   </commentList>

--- a/docs/02-domain/templates/examples/catalog_template_v1_partial.xlsx
+++ b/docs/02-domain/templates/examples/catalog_template_v1_partial.xlsx
@@ -14,7 +14,7 @@
     <sheet name="_System" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Каталог'!$A$1:$J$1000</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Каталог'!$A$1:$L$1000</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -204,7 +204,17 @@
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
-        <t>Список идентификаторов загруженных фотографий через `;` (например «12;15»). Заполняется автоматически карточкой товара — не редактируется вручную.</t>
+        <t>Список идентификаторов загруженных фотографий через `;` (например «12;15»). Заполняется автоматически карточкой товара — не редактируется вручную. Без фото товар сохранится, но покупателю показан не будет — публикация сообщит о таких товарах.</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Страна, из которой привезён товар. Показывается покупателю в карточке товара. Необязательно. Пример: «Марокко».</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Формат ДД.ММ.ГГГГ. Прошедшая дата означает состоявшийся завоз партии — покупатель видит по ней свежесть товара; будущая означает планируемую поставку. Необязательно. Пример: «01.08.2026».</t>
       </text>
     </comment>
   </commentList>
@@ -500,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="16" customWidth="1" min="1" max="1"/>
@@ -513,6 +523,8 @@
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="32" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -566,6 +578,16 @@
           <t>Фото</t>
         </is>
       </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Страна происхождения</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Дата поставки</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="B2" t="inlineStr">
@@ -634,7 +656,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1000"/>
+  <autoFilter ref="A1:L1000"/>
   <dataValidations count="5">
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Неизвестная товарная группа" error="Выберите товарную группу из списка (см. лист «Товарные группы»)" type="list">
       <formula1>"Фрукты,Овощи,Молочные продукты,Мясо,Рыба,Напитки,Цитрусовые,Яблоки,Бананы,Томаты,Огурцы,Картофель,Молоко,Сыр,Йогурты"</formula1>
@@ -1254,7 +1276,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
     </row>

--- a/docs/02-domain/templates/examples/catalog_template_v1_partial.xlsx
+++ b/docs/02-domain/templates/examples/catalog_template_v1_partial.xlsx
@@ -14,7 +14,7 @@
     <sheet name="_System" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Каталог'!$A$1:$L$1000</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Каталог'!$A$1:$M$1000</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -215,6 +215,11 @@
     <comment ref="L1" authorId="0" shapeId="0">
       <text>
         <t>Формат ДД.ММ.ГГГГ. Прошедшая дата означает состоявшийся завоз партии — покупатель видит по ней свежесть товара; будущая означает планируемую поставку. Необязательно. Пример: «01.08.2026».</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>Ваш собственный код товара, уникальный внутри вашего каталога. По нему GreenMarket узнаёт строку при повторной публикации: с артикулом товар обновляется, без артикула — создаётся заново. Заполняйте у каждого товара и не меняйте потом — смена артикула считается новым товаром. Покупателю не показывается. Пример: «PROD-1001».</t>
       </text>
     </comment>
   </commentList>
@@ -510,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="16" customWidth="1" min="1" max="1"/>
@@ -525,6 +530,7 @@
     <col width="40" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -588,6 +594,11 @@
           <t>Дата поставки</t>
         </is>
       </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Артикул продавца</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="B2" t="inlineStr">
@@ -656,7 +667,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1000"/>
+  <autoFilter ref="A1:M1000"/>
   <dataValidations count="5">
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Неизвестная товарная группа" error="Выберите товарную группу из списка (см. лист «Товарные группы»)" type="list">
       <formula1>"Фрукты,Овощи,Молочные продукты,Мясо,Рыба,Напитки,Цитрусовые,Яблоки,Бананы,Томаты,Огурцы,Картофель,Молоко,Сыр,Йогурты"</formula1>
@@ -1276,7 +1287,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
     </row>
